--- a/uploads/room_mapping.xlsx
+++ b/uploads/room_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33A4811-A1EC-4ED0-B393-2DCE33D98BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50646E9-BBFF-45AA-BFC2-096965993B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F2E3252-A846-4A0E-8072-090428F4B060}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>S6_CSE_A</t>
   </si>
@@ -167,22 +167,10 @@
     <t>A305</t>
   </si>
   <si>
-    <t>B406</t>
-  </si>
-  <si>
     <t>A401</t>
   </si>
   <si>
     <t>A513</t>
-  </si>
-  <si>
-    <t>B407</t>
-  </si>
-  <si>
-    <t>B409</t>
-  </si>
-  <si>
-    <t>B405</t>
   </si>
   <si>
     <t>A512</t>
@@ -557,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3935CA-7760-4391-810A-C3351C5882AD}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -815,38 +803,6 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28">
-        <v>70</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
